--- a/songs/BloodyMary_v1/quelle/struktur-raster.xlsx
+++ b/songs/BloodyMary_v1/quelle/struktur-raster.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6" collapsed="1">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="4" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
@@ -570,7 +570,7 @@
     </row>
     <row r="8" hidden="1" outlineLevel="2">
       <c r="A8" s="4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
@@ -581,7 +581,7 @@
     </row>
     <row r="9" hidden="1" outlineLevel="2">
       <c r="A9" s="4" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
@@ -592,7 +592,7 @@
     </row>
     <row r="10" collapsed="1">
       <c r="A10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
     </row>
     <row r="11" hidden="1" outlineLevel="2">
       <c r="A11" s="4" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
@@ -630,7 +630,7 @@
     </row>
     <row r="12" hidden="1" outlineLevel="2">
       <c r="A12" s="4" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="n"/>
@@ -641,7 +641,7 @@
     </row>
     <row r="13" hidden="1" outlineLevel="2">
       <c r="A13" s="4" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6" t="n"/>
@@ -652,7 +652,7 @@
     </row>
     <row r="14" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="n"/>
@@ -663,7 +663,7 @@
     </row>
     <row r="15" hidden="1" outlineLevel="2">
       <c r="A15" s="4" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
@@ -674,7 +674,7 @@
     </row>
     <row r="16" hidden="1" outlineLevel="2">
       <c r="A16" s="4" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
@@ -685,7 +685,7 @@
     </row>
     <row r="17" hidden="1" outlineLevel="2">
       <c r="A17" s="4" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="n"/>
@@ -696,7 +696,7 @@
     </row>
     <row r="18" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="n"/>
@@ -707,7 +707,7 @@
     </row>
     <row r="19" hidden="1" outlineLevel="2">
       <c r="A19" s="4" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
@@ -718,7 +718,7 @@
     </row>
     <row r="20" hidden="1" outlineLevel="2">
       <c r="A20" s="4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="n"/>
@@ -729,7 +729,7 @@
     </row>
     <row r="21" hidden="1" outlineLevel="2">
       <c r="A21" s="4" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="n"/>
@@ -740,7 +740,7 @@
     </row>
     <row r="22" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="n"/>
@@ -751,7 +751,7 @@
     </row>
     <row r="23" hidden="1" outlineLevel="2">
       <c r="A23" s="4" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="24" hidden="1" outlineLevel="2">
       <c r="A24" s="4" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="n"/>
@@ -773,7 +773,7 @@
     </row>
     <row r="25" hidden="1" outlineLevel="2">
       <c r="A25" s="4" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="n"/>
@@ -784,7 +784,7 @@
     </row>
     <row r="26" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="n"/>
@@ -795,7 +795,7 @@
     </row>
     <row r="27" hidden="1" outlineLevel="2">
       <c r="A27" s="4" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="n"/>
@@ -806,7 +806,7 @@
     </row>
     <row r="28" hidden="1" outlineLevel="2">
       <c r="A28" s="4" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="n"/>
@@ -817,7 +817,7 @@
     </row>
     <row r="29" hidden="1" outlineLevel="2">
       <c r="A29" s="4" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="n"/>
@@ -828,7 +828,7 @@
     </row>
     <row r="30" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A30" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="n"/>
@@ -839,7 +839,7 @@
     </row>
     <row r="31" hidden="1" outlineLevel="2">
       <c r="A31" s="4" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="n"/>
@@ -850,7 +850,7 @@
     </row>
     <row r="32" hidden="1" outlineLevel="2">
       <c r="A32" s="4" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="n"/>
@@ -861,7 +861,7 @@
     </row>
     <row r="33" hidden="1" outlineLevel="2">
       <c r="A33" s="4" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="n"/>
@@ -872,7 +872,7 @@
     </row>
     <row r="34" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A34" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="n"/>
@@ -883,7 +883,7 @@
     </row>
     <row r="35" hidden="1" outlineLevel="2">
       <c r="A35" s="4" t="n">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="n"/>
@@ -894,7 +894,7 @@
     </row>
     <row r="36" hidden="1" outlineLevel="2">
       <c r="A36" s="4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="n"/>
@@ -905,7 +905,7 @@
     </row>
     <row r="37" hidden="1" outlineLevel="2">
       <c r="A37" s="4" t="n">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="n"/>
@@ -916,7 +916,7 @@
     </row>
     <row r="38" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A38" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="n"/>
@@ -927,7 +927,7 @@
     </row>
     <row r="39" hidden="1" outlineLevel="2">
       <c r="A39" s="4" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="n"/>
@@ -938,7 +938,7 @@
     </row>
     <row r="40" hidden="1" outlineLevel="2">
       <c r="A40" s="4" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="n"/>
@@ -949,7 +949,7 @@
     </row>
     <row r="41" hidden="1" outlineLevel="2">
       <c r="A41" s="4" t="n">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="n"/>
@@ -960,7 +960,7 @@
     </row>
     <row r="42" collapsed="1">
       <c r="A42" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     </row>
     <row r="43" hidden="1" outlineLevel="2">
       <c r="A43" s="4" t="n">
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6" t="n"/>
@@ -998,7 +998,7 @@
     </row>
     <row r="44" hidden="1" outlineLevel="2">
       <c r="A44" s="4" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6" t="n"/>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="45" hidden="1" outlineLevel="2">
       <c r="A45" s="4" t="n">
-        <v>9.75</v>
+        <v>10.75</v>
       </c>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6" t="n"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="46" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A46" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6" t="n"/>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="47" hidden="1" outlineLevel="2">
       <c r="A47" s="4" t="n">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6" t="n"/>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="48" hidden="1" outlineLevel="2">
       <c r="A48" s="4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6" t="n"/>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="49" hidden="1" outlineLevel="2">
       <c r="A49" s="4" t="n">
-        <v>10.75</v>
+        <v>11.75</v>
       </c>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6" t="n"/>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="50" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A50" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6" t="n"/>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="51" hidden="1" outlineLevel="2">
       <c r="A51" s="4" t="n">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6" t="n"/>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="52" hidden="1" outlineLevel="2">
       <c r="A52" s="4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6" t="n"/>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="53" hidden="1" outlineLevel="2">
       <c r="A53" s="4" t="n">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6" t="n"/>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="54" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A54" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6" t="n"/>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="55" hidden="1" outlineLevel="2">
       <c r="A55" s="4" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6" t="n"/>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="56" hidden="1" outlineLevel="2">
       <c r="A56" s="4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6" t="n"/>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="57" hidden="1" outlineLevel="2">
       <c r="A57" s="4" t="n">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6" t="n"/>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="58" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A58" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6" t="n"/>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="59" hidden="1" outlineLevel="2">
       <c r="A59" s="4" t="n">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6" t="n"/>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="60" hidden="1" outlineLevel="2">
       <c r="A60" s="4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6" t="n"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="61" hidden="1" outlineLevel="2">
       <c r="A61" s="4" t="n">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6" t="n"/>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="62" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A62" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6" t="n"/>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="63" hidden="1" outlineLevel="2">
       <c r="A63" s="4" t="n">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6" t="n"/>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="64" hidden="1" outlineLevel="2">
       <c r="A64" s="4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6" t="n"/>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="65" hidden="1" outlineLevel="2">
       <c r="A65" s="4" t="n">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6" t="n"/>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="66" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A66" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6" t="n"/>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="67" hidden="1" outlineLevel="2">
       <c r="A67" s="4" t="n">
-        <v>15.25</v>
+        <v>16.25</v>
       </c>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6" t="n"/>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="68" hidden="1" outlineLevel="2">
       <c r="A68" s="4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6" t="n"/>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="69" hidden="1" outlineLevel="2">
       <c r="A69" s="4" t="n">
-        <v>15.75</v>
+        <v>16.75</v>
       </c>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6" t="n"/>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="70" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A70" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6" t="n"/>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="71" hidden="1" outlineLevel="2">
       <c r="A71" s="4" t="n">
-        <v>16.25</v>
+        <v>17.25</v>
       </c>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6" t="n"/>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="72" hidden="1" outlineLevel="2">
       <c r="A72" s="4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6" t="n"/>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="73" hidden="1" outlineLevel="2">
       <c r="A73" s="4" t="n">
-        <v>16.75</v>
+        <v>17.75</v>
       </c>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6" t="n"/>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="74" collapsed="1">
       <c r="A74" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="75" hidden="1" outlineLevel="2">
       <c r="A75" s="4" t="n">
-        <v>17.25</v>
+        <v>18.25</v>
       </c>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6" t="n"/>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="76" hidden="1" outlineLevel="2">
       <c r="A76" s="4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6" t="n"/>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="77" hidden="1" outlineLevel="2">
       <c r="A77" s="4" t="n">
-        <v>17.75</v>
+        <v>18.75</v>
       </c>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6" t="n"/>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="78" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A78" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6" t="n"/>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="79" hidden="1" outlineLevel="2">
       <c r="A79" s="4" t="n">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6" t="n"/>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="80" hidden="1" outlineLevel="2">
       <c r="A80" s="4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6" t="n"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="81" hidden="1" outlineLevel="2">
       <c r="A81" s="4" t="n">
-        <v>18.75</v>
+        <v>19.75</v>
       </c>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6" t="n"/>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="82" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A82" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6" t="n"/>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="83" hidden="1" outlineLevel="2">
       <c r="A83" s="4" t="n">
-        <v>19.25</v>
+        <v>20.25</v>
       </c>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6" t="n"/>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="84" hidden="1" outlineLevel="2">
       <c r="A84" s="4" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6" t="n"/>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="85" hidden="1" outlineLevel="2">
       <c r="A85" s="4" t="n">
-        <v>19.75</v>
+        <v>20.75</v>
       </c>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6" t="n"/>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="86" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A86" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6" t="n"/>
@@ -1487,7 +1487,7 @@
     </row>
     <row r="87" hidden="1" outlineLevel="2">
       <c r="A87" s="4" t="n">
-        <v>20.25</v>
+        <v>21.25</v>
       </c>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6" t="n"/>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="88" hidden="1" outlineLevel="2">
       <c r="A88" s="4" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6" t="n"/>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="89" hidden="1" outlineLevel="2">
       <c r="A89" s="4" t="n">
-        <v>20.75</v>
+        <v>21.75</v>
       </c>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6" t="n"/>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="90" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A90" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6" t="n"/>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="91" hidden="1" outlineLevel="2">
       <c r="A91" s="4" t="n">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6" t="n"/>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="92" hidden="1" outlineLevel="2">
       <c r="A92" s="4" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6" t="n"/>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="93" hidden="1" outlineLevel="2">
       <c r="A93" s="4" t="n">
-        <v>21.75</v>
+        <v>22.75</v>
       </c>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6" t="n"/>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="94" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A94" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6" t="n"/>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="95" hidden="1" outlineLevel="2">
       <c r="A95" s="4" t="n">
-        <v>22.25</v>
+        <v>23.25</v>
       </c>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6" t="n"/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="96" hidden="1" outlineLevel="2">
       <c r="A96" s="4" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6" t="n"/>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="97" hidden="1" outlineLevel="2">
       <c r="A97" s="4" t="n">
-        <v>22.75</v>
+        <v>23.75</v>
       </c>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6" t="n"/>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="98" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A98" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6" t="n"/>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="99" hidden="1" outlineLevel="2">
       <c r="A99" s="4" t="n">
-        <v>23.25</v>
+        <v>24.25</v>
       </c>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6" t="n"/>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="100" hidden="1" outlineLevel="2">
       <c r="A100" s="4" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6" t="n"/>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="101" hidden="1" outlineLevel="2">
       <c r="A101" s="4" t="n">
-        <v>23.75</v>
+        <v>24.75</v>
       </c>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6" t="n"/>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="102" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A102" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6" t="n"/>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="103" hidden="1" outlineLevel="2">
       <c r="A103" s="4" t="n">
-        <v>24.25</v>
+        <v>25.25</v>
       </c>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6" t="n"/>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="104" hidden="1" outlineLevel="2">
       <c r="A104" s="4" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6" t="n"/>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="105" hidden="1" outlineLevel="2">
       <c r="A105" s="4" t="n">
-        <v>24.75</v>
+        <v>25.75</v>
       </c>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6" t="n"/>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="106" collapsed="1">
       <c r="A106" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="107" hidden="1" outlineLevel="2">
       <c r="A107" s="4" t="n">
-        <v>25.25</v>
+        <v>26.25</v>
       </c>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6" t="n"/>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="108" hidden="1" outlineLevel="2">
       <c r="A108" s="4" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6" t="n"/>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="109" hidden="1" outlineLevel="2">
       <c r="A109" s="4" t="n">
-        <v>25.75</v>
+        <v>26.75</v>
       </c>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6" t="n"/>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="110" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A110" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6" t="n"/>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="111" hidden="1" outlineLevel="2">
       <c r="A111" s="4" t="n">
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6" t="n"/>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="112" hidden="1" outlineLevel="2">
       <c r="A112" s="4" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6" t="n"/>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="113" hidden="1" outlineLevel="2">
       <c r="A113" s="4" t="n">
-        <v>26.75</v>
+        <v>27.75</v>
       </c>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6" t="n"/>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="114" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A114" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6" t="n"/>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="115" hidden="1" outlineLevel="2">
       <c r="A115" s="4" t="n">
-        <v>27.25</v>
+        <v>28.25</v>
       </c>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6" t="n"/>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="116" hidden="1" outlineLevel="2">
       <c r="A116" s="4" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6" t="n"/>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="117" hidden="1" outlineLevel="2">
       <c r="A117" s="4" t="n">
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6" t="n"/>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="118" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A118" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6" t="n"/>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="119" hidden="1" outlineLevel="2">
       <c r="A119" s="4" t="n">
-        <v>28.25</v>
+        <v>29.25</v>
       </c>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6" t="n"/>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="120" hidden="1" outlineLevel="2">
       <c r="A120" s="4" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6" t="n"/>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="121" hidden="1" outlineLevel="2">
       <c r="A121" s="4" t="n">
-        <v>28.75</v>
+        <v>29.75</v>
       </c>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6" t="n"/>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="122" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A122" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6" t="n"/>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="123" hidden="1" outlineLevel="2">
       <c r="A123" s="4" t="n">
-        <v>29.25</v>
+        <v>30.25</v>
       </c>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6" t="n"/>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="124" hidden="1" outlineLevel="2">
       <c r="A124" s="4" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6" t="n"/>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="125" hidden="1" outlineLevel="2">
       <c r="A125" s="4" t="n">
-        <v>29.75</v>
+        <v>30.75</v>
       </c>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6" t="n"/>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="126" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A126" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6" t="n"/>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="127" hidden="1" outlineLevel="2">
       <c r="A127" s="4" t="n">
-        <v>30.25</v>
+        <v>31.25</v>
       </c>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6" t="n"/>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="128" hidden="1" outlineLevel="2">
       <c r="A128" s="4" t="n">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6" t="n"/>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="129" hidden="1" outlineLevel="2">
       <c r="A129" s="4" t="n">
-        <v>30.75</v>
+        <v>31.75</v>
       </c>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6" t="n"/>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="130" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A130" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6" t="n"/>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="131" hidden="1" outlineLevel="2">
       <c r="A131" s="4" t="n">
-        <v>31.25</v>
+        <v>32.25</v>
       </c>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6" t="n"/>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="132" hidden="1" outlineLevel="2">
       <c r="A132" s="4" t="n">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6" t="n"/>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="133" hidden="1" outlineLevel="2">
       <c r="A133" s="4" t="n">
-        <v>31.75</v>
+        <v>32.75</v>
       </c>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6" t="n"/>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="134" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A134" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6" t="n"/>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="135" hidden="1" outlineLevel="2">
       <c r="A135" s="4" t="n">
-        <v>32.25</v>
+        <v>33.25</v>
       </c>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6" t="n"/>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="136" hidden="1" outlineLevel="2">
       <c r="A136" s="4" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6" t="n"/>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="137" hidden="1" outlineLevel="2">
       <c r="A137" s="4" t="n">
-        <v>32.75</v>
+        <v>33.75</v>
       </c>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6" t="n"/>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="138" collapsed="1">
       <c r="A138" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="139" hidden="1" outlineLevel="2">
       <c r="A139" s="4" t="n">
-        <v>33.25</v>
+        <v>34.25</v>
       </c>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6" t="n"/>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="140" hidden="1" outlineLevel="2">
       <c r="A140" s="4" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6" t="n"/>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="141" hidden="1" outlineLevel="2">
       <c r="A141" s="4" t="n">
-        <v>33.75</v>
+        <v>34.75</v>
       </c>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6" t="n"/>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="142" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A142" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6" t="n"/>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="143" hidden="1" outlineLevel="2">
       <c r="A143" s="4" t="n">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6" t="n"/>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="144" hidden="1" outlineLevel="2">
       <c r="A144" s="4" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6" t="n"/>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="145" hidden="1" outlineLevel="2">
       <c r="A145" s="4" t="n">
-        <v>34.75</v>
+        <v>35.75</v>
       </c>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6" t="n"/>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="146" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A146" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6" t="n"/>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="147" hidden="1" outlineLevel="2">
       <c r="A147" s="4" t="n">
-        <v>35.25</v>
+        <v>36.25</v>
       </c>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6" t="n"/>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="148" hidden="1" outlineLevel="2">
       <c r="A148" s="4" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6" t="n"/>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="149" hidden="1" outlineLevel="2">
       <c r="A149" s="4" t="n">
-        <v>35.75</v>
+        <v>36.75</v>
       </c>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6" t="n"/>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="150" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A150" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6" t="n"/>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="151" hidden="1" outlineLevel="2">
       <c r="A151" s="4" t="n">
-        <v>36.25</v>
+        <v>37.25</v>
       </c>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6" t="n"/>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="152" hidden="1" outlineLevel="2">
       <c r="A152" s="4" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6" t="n"/>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="153" hidden="1" outlineLevel="2">
       <c r="A153" s="4" t="n">
-        <v>36.75</v>
+        <v>37.75</v>
       </c>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6" t="n"/>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="154" collapsed="1">
       <c r="A154" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="155" hidden="1" outlineLevel="2">
       <c r="A155" s="4" t="n">
-        <v>37.25</v>
+        <v>38.25</v>
       </c>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6" t="n"/>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="156" hidden="1" outlineLevel="2">
       <c r="A156" s="4" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6" t="n"/>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="157" hidden="1" outlineLevel="2">
       <c r="A157" s="4" t="n">
-        <v>37.75</v>
+        <v>38.75</v>
       </c>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6" t="n"/>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="158" collapsed="1">
       <c r="A158" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="159" hidden="1" outlineLevel="2">
       <c r="A159" s="4" t="n">
-        <v>38.25</v>
+        <v>39.25</v>
       </c>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6" t="n"/>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="160" hidden="1" outlineLevel="2">
       <c r="A160" s="4" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6" t="n"/>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="161" hidden="1" outlineLevel="2">
       <c r="A161" s="4" t="n">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6" t="n"/>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="162" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A162" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6" t="n"/>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="163" hidden="1" outlineLevel="2">
       <c r="A163" s="4" t="n">
-        <v>39.25</v>
+        <v>40.25</v>
       </c>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6" t="n"/>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="164" hidden="1" outlineLevel="2">
       <c r="A164" s="4" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6" t="n"/>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="165" hidden="1" outlineLevel="2">
       <c r="A165" s="4" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6" t="n"/>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="166" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A166" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6" t="n"/>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="167" hidden="1" outlineLevel="2">
       <c r="A167" s="4" t="n">
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6" t="n"/>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="168" hidden="1" outlineLevel="2">
       <c r="A168" s="4" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6" t="n"/>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="169" hidden="1" outlineLevel="2">
       <c r="A169" s="4" t="n">
-        <v>40.75</v>
+        <v>41.75</v>
       </c>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="n"/>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="170" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A170" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6" t="n"/>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="171" hidden="1" outlineLevel="2">
       <c r="A171" s="4" t="n">
-        <v>41.25</v>
+        <v>42.25</v>
       </c>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6" t="n"/>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="172" hidden="1" outlineLevel="2">
       <c r="A172" s="4" t="n">
-        <v>41.5</v>
+        <v>42.5</v>
       </c>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6" t="n"/>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="173" hidden="1" outlineLevel="2">
       <c r="A173" s="4" t="n">
-        <v>41.75</v>
+        <v>42.75</v>
       </c>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6" t="n"/>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="174" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A174" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6" t="n"/>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="175" hidden="1" outlineLevel="2">
       <c r="A175" s="4" t="n">
-        <v>42.25</v>
+        <v>43.25</v>
       </c>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6" t="n"/>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="176" hidden="1" outlineLevel="2">
       <c r="A176" s="4" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6" t="n"/>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="177" hidden="1" outlineLevel="2">
       <c r="A177" s="4" t="n">
-        <v>42.75</v>
+        <v>43.75</v>
       </c>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6" t="n"/>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="178" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A178" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6" t="n"/>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="179" hidden="1" outlineLevel="2">
       <c r="A179" s="4" t="n">
-        <v>43.25</v>
+        <v>44.25</v>
       </c>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6" t="n"/>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="180" hidden="1" outlineLevel="2">
       <c r="A180" s="4" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6" t="n"/>
@@ -2585,7 +2585,7 @@
     </row>
     <row r="181" hidden="1" outlineLevel="2">
       <c r="A181" s="4" t="n">
-        <v>43.75</v>
+        <v>44.75</v>
       </c>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6" t="n"/>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="182" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A182" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6" t="n"/>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="183" hidden="1" outlineLevel="2">
       <c r="A183" s="4" t="n">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6" t="n"/>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="184" hidden="1" outlineLevel="2">
       <c r="A184" s="4" t="n">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6" t="n"/>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="185" hidden="1" outlineLevel="2">
       <c r="A185" s="4" t="n">
-        <v>44.75</v>
+        <v>45.75</v>
       </c>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6" t="n"/>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="186" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A186" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6" t="n"/>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="187" hidden="1" outlineLevel="2">
       <c r="A187" s="4" t="n">
-        <v>45.25</v>
+        <v>46.25</v>
       </c>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6" t="n"/>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="188" hidden="1" outlineLevel="2">
       <c r="A188" s="4" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6" t="n"/>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="189" hidden="1" outlineLevel="2">
       <c r="A189" s="4" t="n">
-        <v>45.75</v>
+        <v>46.75</v>
       </c>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6" t="n"/>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="190" collapsed="1">
       <c r="A190" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="191" hidden="1" outlineLevel="2">
       <c r="A191" s="4" t="n">
-        <v>46.25</v>
+        <v>47.25</v>
       </c>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6" t="n"/>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="192" hidden="1" outlineLevel="2">
       <c r="A192" s="4" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6" t="n"/>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="193" hidden="1" outlineLevel="2">
       <c r="A193" s="4" t="n">
-        <v>46.75</v>
+        <v>47.75</v>
       </c>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6" t="n"/>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="194" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A194" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6" t="n"/>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="195" hidden="1" outlineLevel="2">
       <c r="A195" s="4" t="n">
-        <v>47.25</v>
+        <v>48.25</v>
       </c>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6" t="n"/>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="196" hidden="1" outlineLevel="2">
       <c r="A196" s="4" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6" t="n"/>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="197" hidden="1" outlineLevel="2">
       <c r="A197" s="4" t="n">
-        <v>47.75</v>
+        <v>48.75</v>
       </c>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6" t="n"/>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="198" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A198" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6" t="n"/>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="199" hidden="1" outlineLevel="2">
       <c r="A199" s="4" t="n">
-        <v>48.25</v>
+        <v>49.25</v>
       </c>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6" t="n"/>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="200" hidden="1" outlineLevel="2">
       <c r="A200" s="4" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6" t="n"/>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="201" hidden="1" outlineLevel="2">
       <c r="A201" s="4" t="n">
-        <v>48.75</v>
+        <v>49.75</v>
       </c>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6" t="n"/>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="202" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A202" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6" t="n"/>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="203" hidden="1" outlineLevel="2">
       <c r="A203" s="4" t="n">
-        <v>49.25</v>
+        <v>50.25</v>
       </c>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6" t="n"/>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="204" hidden="1" outlineLevel="2">
       <c r="A204" s="4" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6" t="n"/>
@@ -2865,7 +2865,7 @@
     </row>
     <row r="205" hidden="1" outlineLevel="2">
       <c r="A205" s="4" t="n">
-        <v>49.75</v>
+        <v>50.75</v>
       </c>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6" t="n"/>
@@ -2876,7 +2876,7 @@
     </row>
     <row r="206" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A206" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6" t="n"/>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="207" hidden="1" outlineLevel="2">
       <c r="A207" s="4" t="n">
-        <v>50.25</v>
+        <v>51.25</v>
       </c>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6" t="n"/>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="208" hidden="1" outlineLevel="2">
       <c r="A208" s="4" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6" t="n"/>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="209" hidden="1" outlineLevel="2">
       <c r="A209" s="4" t="n">
-        <v>50.75</v>
+        <v>51.75</v>
       </c>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6" t="n"/>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="210" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A210" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6" t="n"/>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="211" hidden="1" outlineLevel="2">
       <c r="A211" s="4" t="n">
-        <v>51.25</v>
+        <v>52.25</v>
       </c>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6" t="n"/>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="212" hidden="1" outlineLevel="2">
       <c r="A212" s="4" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6" t="n"/>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="213" hidden="1" outlineLevel="2">
       <c r="A213" s="4" t="n">
-        <v>51.75</v>
+        <v>52.75</v>
       </c>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6" t="n"/>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="214" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A214" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6" t="n"/>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="215" hidden="1" outlineLevel="2">
       <c r="A215" s="4" t="n">
-        <v>52.25</v>
+        <v>53.25</v>
       </c>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6" t="n"/>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="216" hidden="1" outlineLevel="2">
       <c r="A216" s="4" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6" t="n"/>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="217" hidden="1" outlineLevel="2">
       <c r="A217" s="4" t="n">
-        <v>52.75</v>
+        <v>53.75</v>
       </c>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6" t="n"/>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="218" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A218" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6" t="n"/>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="219" hidden="1" outlineLevel="2">
       <c r="A219" s="4" t="n">
-        <v>53.25</v>
+        <v>54.25</v>
       </c>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6" t="n"/>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="220" hidden="1" outlineLevel="2">
       <c r="A220" s="4" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6" t="n"/>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="221" hidden="1" outlineLevel="2">
       <c r="A221" s="4" t="n">
-        <v>53.75</v>
+        <v>54.75</v>
       </c>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6" t="n"/>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="222" collapsed="1">
       <c r="A222" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="223" hidden="1" outlineLevel="2">
       <c r="A223" s="4" t="n">
-        <v>54.25</v>
+        <v>55.25</v>
       </c>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6" t="n"/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="224" hidden="1" outlineLevel="2">
       <c r="A224" s="4" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6" t="n"/>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="225" hidden="1" outlineLevel="2">
       <c r="A225" s="4" t="n">
-        <v>54.75</v>
+        <v>55.75</v>
       </c>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6" t="n"/>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="226" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A226" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6" t="n"/>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="227" hidden="1" outlineLevel="2">
       <c r="A227" s="4" t="n">
-        <v>55.25</v>
+        <v>56.25</v>
       </c>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6" t="n"/>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="228" hidden="1" outlineLevel="2">
       <c r="A228" s="4" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6" t="n"/>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="229" hidden="1" outlineLevel="2">
       <c r="A229" s="4" t="n">
-        <v>55.75</v>
+        <v>56.75</v>
       </c>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6" t="n"/>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="230" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A230" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6" t="n"/>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="231" hidden="1" outlineLevel="2">
       <c r="A231" s="4" t="n">
-        <v>56.25</v>
+        <v>57.25</v>
       </c>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6" t="n"/>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="232" hidden="1" outlineLevel="2">
       <c r="A232" s="4" t="n">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6" t="n"/>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="233" hidden="1" outlineLevel="2">
       <c r="A233" s="4" t="n">
-        <v>56.75</v>
+        <v>57.75</v>
       </c>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6" t="n"/>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="234" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A234" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6" t="n"/>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="235" hidden="1" outlineLevel="2">
       <c r="A235" s="4" t="n">
-        <v>57.25</v>
+        <v>58.25</v>
       </c>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6" t="n"/>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="236" hidden="1" outlineLevel="2">
       <c r="A236" s="4" t="n">
-        <v>57.5</v>
+        <v>58.5</v>
       </c>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6" t="n"/>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="237" hidden="1" outlineLevel="2">
       <c r="A237" s="4" t="n">
-        <v>57.75</v>
+        <v>58.75</v>
       </c>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6" t="n"/>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="238" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A238" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6" t="n"/>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="239" hidden="1" outlineLevel="2">
       <c r="A239" s="4" t="n">
-        <v>58.25</v>
+        <v>59.25</v>
       </c>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6" t="n"/>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="240" hidden="1" outlineLevel="2">
       <c r="A240" s="4" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6" t="n"/>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="241" hidden="1" outlineLevel="2">
       <c r="A241" s="4" t="n">
-        <v>58.75</v>
+        <v>59.75</v>
       </c>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6" t="n"/>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="242" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A242" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6" t="n"/>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="243" hidden="1" outlineLevel="2">
       <c r="A243" s="4" t="n">
-        <v>59.25</v>
+        <v>60.25</v>
       </c>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6" t="n"/>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="244" hidden="1" outlineLevel="2">
       <c r="A244" s="4" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6" t="n"/>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="245" hidden="1" outlineLevel="2">
       <c r="A245" s="4" t="n">
-        <v>59.75</v>
+        <v>60.75</v>
       </c>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6" t="n"/>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="246" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A246" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6" t="n"/>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="247" hidden="1" outlineLevel="2">
       <c r="A247" s="4" t="n">
-        <v>60.25</v>
+        <v>61.25</v>
       </c>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6" t="n"/>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="248" hidden="1" outlineLevel="2">
       <c r="A248" s="4" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6" t="n"/>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="249" hidden="1" outlineLevel="2">
       <c r="A249" s="4" t="n">
-        <v>60.75</v>
+        <v>61.75</v>
       </c>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6" t="n"/>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="250" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A250" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6" t="n"/>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="251" hidden="1" outlineLevel="2">
       <c r="A251" s="4" t="n">
-        <v>61.25</v>
+        <v>62.25</v>
       </c>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6" t="n"/>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="252" hidden="1" outlineLevel="2">
       <c r="A252" s="4" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6" t="n"/>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="253" hidden="1" outlineLevel="2">
       <c r="A253" s="4" t="n">
-        <v>61.75</v>
+        <v>62.75</v>
       </c>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6" t="n"/>
@@ -3420,7 +3420,7 @@
     </row>
     <row r="254" collapsed="1">
       <c r="A254" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="255" hidden="1" outlineLevel="2">
       <c r="A255" s="4" t="n">
-        <v>62.25</v>
+        <v>63.25</v>
       </c>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6" t="n"/>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="256" hidden="1" outlineLevel="2">
       <c r="A256" s="4" t="n">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6" t="n"/>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="257" hidden="1" outlineLevel="2">
       <c r="A257" s="4" t="n">
-        <v>62.75</v>
+        <v>63.75</v>
       </c>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6" t="n"/>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="258" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A258" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6" t="n"/>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="259" hidden="1" outlineLevel="2">
       <c r="A259" s="4" t="n">
-        <v>63.25</v>
+        <v>64.25</v>
       </c>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6" t="n"/>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="260" hidden="1" outlineLevel="2">
       <c r="A260" s="4" t="n">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6" t="n"/>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="261" hidden="1" outlineLevel="2">
       <c r="A261" s="4" t="n">
-        <v>63.75</v>
+        <v>64.75</v>
       </c>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6" t="n"/>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="262" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A262" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6" t="n"/>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="263" hidden="1" outlineLevel="2">
       <c r="A263" s="4" t="n">
-        <v>64.25</v>
+        <v>65.25</v>
       </c>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6" t="n"/>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="264" hidden="1" outlineLevel="2">
       <c r="A264" s="4" t="n">
-        <v>64.5</v>
+        <v>65.5</v>
       </c>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6" t="n"/>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="265" hidden="1" outlineLevel="2">
       <c r="A265" s="4" t="n">
-        <v>64.75</v>
+        <v>65.75</v>
       </c>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6" t="n"/>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="266" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A266" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6" t="n"/>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="267" hidden="1" outlineLevel="2">
       <c r="A267" s="4" t="n">
-        <v>65.25</v>
+        <v>66.25</v>
       </c>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6" t="n"/>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="268" hidden="1" outlineLevel="2">
       <c r="A268" s="4" t="n">
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6" t="n"/>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="269" hidden="1" outlineLevel="2">
       <c r="A269" s="4" t="n">
-        <v>65.75</v>
+        <v>66.75</v>
       </c>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6" t="n"/>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="270" collapsed="1">
       <c r="A270" s="4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="271" hidden="1" outlineLevel="2">
       <c r="A271" s="4" t="n">
-        <v>66.25</v>
+        <v>67.25</v>
       </c>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6" t="n"/>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="272" collapsed="1">
       <c r="A272" s="4" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="273" hidden="1" outlineLevel="2">
       <c r="A273" s="4" t="n">
-        <v>66.75</v>
+        <v>67.75</v>
       </c>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6" t="n"/>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="274" collapsed="1">
       <c r="A274" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="275" hidden="1" outlineLevel="2">
       <c r="A275" s="4" t="n">
-        <v>67.25</v>
+        <v>68.25</v>
       </c>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6" t="n"/>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="276" collapsed="1">
       <c r="A276" s="4" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="277" hidden="1" outlineLevel="2">
       <c r="A277" s="4" t="n">
-        <v>67.75</v>
+        <v>68.75</v>
       </c>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6" t="n"/>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="278" collapsed="1">
       <c r="A278" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="279" hidden="1" outlineLevel="2">
       <c r="A279" s="4" t="n">
-        <v>68.25</v>
+        <v>69.25</v>
       </c>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6" t="n"/>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="280" collapsed="1">
       <c r="A280" s="4" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="281" hidden="1" outlineLevel="2">
       <c r="A281" s="4" t="n">
-        <v>68.75</v>
+        <v>69.75</v>
       </c>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6" t="n"/>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="282" collapsed="1">
       <c r="A282" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="283" hidden="1" outlineLevel="2">
       <c r="A283" s="4" t="n">
-        <v>69.25</v>
+        <v>70.25</v>
       </c>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6" t="n"/>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="284" collapsed="1">
       <c r="A284" s="4" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
     </row>
     <row r="285" hidden="1" outlineLevel="2">
       <c r="A285" s="4" t="n">
-        <v>69.75</v>
+        <v>70.75</v>
       </c>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6" t="n"/>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="286" collapsed="1">
       <c r="A286" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="287" hidden="1" outlineLevel="2">
       <c r="A287" s="4" t="n">
-        <v>70.25</v>
+        <v>71.25</v>
       </c>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6" t="n"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="288" collapsed="1">
       <c r="A288" s="4" t="n">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
     </row>
     <row r="289" hidden="1" outlineLevel="2">
       <c r="A289" s="4" t="n">
-        <v>70.75</v>
+        <v>71.75</v>
       </c>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6" t="n"/>
@@ -3992,7 +3992,7 @@
     </row>
     <row r="290" collapsed="1">
       <c r="A290" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
     </row>
     <row r="291" hidden="1" outlineLevel="2">
       <c r="A291" s="4" t="n">
-        <v>71.25</v>
+        <v>72.25</v>
       </c>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6" t="n"/>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="292" collapsed="1">
       <c r="A292" s="4" t="n">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="293" hidden="1" outlineLevel="2">
       <c r="A293" s="4" t="n">
-        <v>71.75</v>
+        <v>72.75</v>
       </c>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6" t="n"/>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="294" collapsed="1">
       <c r="A294" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="295" hidden="1" outlineLevel="2">
       <c r="A295" s="4" t="n">
-        <v>72.25</v>
+        <v>73.25</v>
       </c>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6" t="n"/>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="296" collapsed="1">
       <c r="A296" s="4" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="297" hidden="1" outlineLevel="2">
       <c r="A297" s="4" t="n">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6" t="n"/>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="298" collapsed="1">
       <c r="A298" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="299" hidden="1" outlineLevel="2">
       <c r="A299" s="4" t="n">
-        <v>73.25</v>
+        <v>74.25</v>
       </c>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6" t="n"/>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="300" collapsed="1">
       <c r="A300" s="4" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="301" hidden="1" outlineLevel="2">
       <c r="A301" s="4" t="n">
-        <v>73.75</v>
+        <v>74.75</v>
       </c>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6" t="n"/>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="302" collapsed="1">
       <c r="A302" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="303" hidden="1" outlineLevel="2">
       <c r="A303" s="4" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6" t="n"/>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="304" hidden="1" outlineLevel="2">
       <c r="A304" s="4" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6" t="n"/>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="305" hidden="1" outlineLevel="2">
       <c r="A305" s="4" t="n">
-        <v>74.75</v>
+        <v>75.75</v>
       </c>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6" t="n"/>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="306" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A306" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6" t="n"/>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="307" hidden="1" outlineLevel="2">
       <c r="A307" s="4" t="n">
-        <v>75.25</v>
+        <v>76.25</v>
       </c>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6" t="n"/>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="308" hidden="1" outlineLevel="2">
       <c r="A308" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6" t="n"/>
@@ -4313,7 +4313,7 @@
     </row>
     <row r="309" hidden="1" outlineLevel="2">
       <c r="A309" s="4" t="n">
-        <v>75.75</v>
+        <v>76.75</v>
       </c>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6" t="n"/>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="310" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A310" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6" t="n"/>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="311" hidden="1" outlineLevel="2">
       <c r="A311" s="4" t="n">
-        <v>76.25</v>
+        <v>77.25</v>
       </c>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6" t="n"/>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="312" hidden="1" outlineLevel="2">
       <c r="A312" s="4" t="n">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6" t="n"/>
@@ -4357,7 +4357,7 @@
     </row>
     <row r="313" hidden="1" outlineLevel="2">
       <c r="A313" s="4" t="n">
-        <v>76.75</v>
+        <v>77.75</v>
       </c>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6" t="n"/>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="314" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A314" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6" t="n"/>
@@ -4379,7 +4379,7 @@
     </row>
     <row r="315" hidden="1" outlineLevel="2">
       <c r="A315" s="4" t="n">
-        <v>77.25</v>
+        <v>78.25</v>
       </c>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6" t="n"/>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="316" hidden="1" outlineLevel="2">
       <c r="A316" s="4" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6" t="n"/>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="317" hidden="1" outlineLevel="2">
       <c r="A317" s="4" t="n">
-        <v>77.75</v>
+        <v>78.75</v>
       </c>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6" t="n"/>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="318" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A318" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6" t="n"/>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="319" hidden="1" outlineLevel="2">
       <c r="A319" s="4" t="n">
-        <v>78.25</v>
+        <v>79.25</v>
       </c>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6" t="n"/>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="320" hidden="1" outlineLevel="2">
       <c r="A320" s="4" t="n">
-        <v>78.5</v>
+        <v>79.5</v>
       </c>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6" t="n"/>
@@ -4445,7 +4445,7 @@
     </row>
     <row r="321" hidden="1" outlineLevel="2">
       <c r="A321" s="4" t="n">
-        <v>78.75</v>
+        <v>79.75</v>
       </c>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6" t="n"/>
@@ -4456,7 +4456,7 @@
     </row>
     <row r="322" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A322" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6" t="n"/>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="323" hidden="1" outlineLevel="2">
       <c r="A323" s="4" t="n">
-        <v>79.25</v>
+        <v>80.25</v>
       </c>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6" t="n"/>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="324" hidden="1" outlineLevel="2">
       <c r="A324" s="4" t="n">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6" t="n"/>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="325" hidden="1" outlineLevel="2">
       <c r="A325" s="4" t="n">
-        <v>79.75</v>
+        <v>80.75</v>
       </c>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6" t="n"/>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="326" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A326" s="4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6" t="n"/>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="327" hidden="1" outlineLevel="2">
       <c r="A327" s="4" t="n">
-        <v>80.25</v>
+        <v>81.25</v>
       </c>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6" t="n"/>
@@ -4522,7 +4522,7 @@
     </row>
     <row r="328" hidden="1" outlineLevel="2">
       <c r="A328" s="4" t="n">
-        <v>80.5</v>
+        <v>81.5</v>
       </c>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6" t="n"/>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="329" hidden="1" outlineLevel="2">
       <c r="A329" s="4" t="n">
-        <v>80.75</v>
+        <v>81.75</v>
       </c>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6" t="n"/>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="330" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A330" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6" t="n"/>
@@ -4555,7 +4555,7 @@
     </row>
     <row r="331" hidden="1" outlineLevel="2">
       <c r="A331" s="4" t="n">
-        <v>81.25</v>
+        <v>82.25</v>
       </c>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6" t="n"/>
@@ -4566,7 +4566,7 @@
     </row>
     <row r="332" hidden="1" outlineLevel="2">
       <c r="A332" s="4" t="n">
-        <v>81.5</v>
+        <v>82.5</v>
       </c>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6" t="n"/>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="333" hidden="1" outlineLevel="2">
       <c r="A333" s="4" t="n">
-        <v>81.75</v>
+        <v>82.75</v>
       </c>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6" t="n"/>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="334" collapsed="1">
       <c r="A334" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B334" s="5" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="335" hidden="1" outlineLevel="2">
       <c r="A335" s="4" t="n">
-        <v>82.25</v>
+        <v>83.25</v>
       </c>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6" t="n"/>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="336" hidden="1" outlineLevel="2">
       <c r="A336" s="4" t="n">
-        <v>82.5</v>
+        <v>83.5</v>
       </c>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6" t="n"/>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="337" hidden="1" outlineLevel="2">
       <c r="A337" s="4" t="n">
-        <v>82.75</v>
+        <v>83.75</v>
       </c>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6" t="n"/>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="338" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A338" s="4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6" t="n"/>
@@ -4659,7 +4659,7 @@
     </row>
     <row r="339" hidden="1" outlineLevel="2">
       <c r="A339" s="4" t="n">
-        <v>83.25</v>
+        <v>84.25</v>
       </c>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6" t="n"/>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="340" hidden="1" outlineLevel="2">
       <c r="A340" s="4" t="n">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6" t="n"/>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="341" hidden="1" outlineLevel="2">
       <c r="A341" s="4" t="n">
-        <v>83.75</v>
+        <v>84.75</v>
       </c>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6" t="n"/>
@@ -4692,7 +4692,7 @@
     </row>
     <row r="342" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A342" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6" t="n"/>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="343" hidden="1" outlineLevel="2">
       <c r="A343" s="4" t="n">
-        <v>84.25</v>
+        <v>85.25</v>
       </c>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6" t="n"/>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="344" hidden="1" outlineLevel="2">
       <c r="A344" s="4" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6" t="n"/>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="345" hidden="1" outlineLevel="2">
       <c r="A345" s="4" t="n">
-        <v>84.75</v>
+        <v>85.75</v>
       </c>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6" t="n"/>
@@ -4736,7 +4736,7 @@
     </row>
     <row r="346" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A346" s="4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6" t="n"/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="347" hidden="1" outlineLevel="2">
       <c r="A347" s="4" t="n">
-        <v>85.25</v>
+        <v>86.25</v>
       </c>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6" t="n"/>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="348" hidden="1" outlineLevel="2">
       <c r="A348" s="4" t="n">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6" t="n"/>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="349" hidden="1" outlineLevel="2">
       <c r="A349" s="4" t="n">
-        <v>85.75</v>
+        <v>86.75</v>
       </c>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6" t="n"/>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="350" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A350" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6" t="n"/>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="351" hidden="1" outlineLevel="2">
       <c r="A351" s="4" t="n">
-        <v>86.25</v>
+        <v>87.25</v>
       </c>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6" t="n"/>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="352" hidden="1" outlineLevel="2">
       <c r="A352" s="4" t="n">
-        <v>86.5</v>
+        <v>87.5</v>
       </c>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6" t="n"/>
@@ -4813,7 +4813,7 @@
     </row>
     <row r="353" hidden="1" outlineLevel="2">
       <c r="A353" s="4" t="n">
-        <v>86.75</v>
+        <v>87.75</v>
       </c>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6" t="n"/>
@@ -4824,7 +4824,7 @@
     </row>
     <row r="354" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A354" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6" t="n"/>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="355" hidden="1" outlineLevel="2">
       <c r="A355" s="4" t="n">
-        <v>87.25</v>
+        <v>88.25</v>
       </c>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6" t="n"/>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="356" hidden="1" outlineLevel="2">
       <c r="A356" s="4" t="n">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6" t="n"/>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="357" hidden="1" outlineLevel="2">
       <c r="A357" s="4" t="n">
-        <v>87.75</v>
+        <v>88.75</v>
       </c>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6" t="n"/>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="358" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A358" s="4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6" t="n"/>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="359" hidden="1" outlineLevel="2">
       <c r="A359" s="4" t="n">
-        <v>88.25</v>
+        <v>89.25</v>
       </c>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6" t="n"/>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="360" hidden="1" outlineLevel="2">
       <c r="A360" s="4" t="n">
-        <v>88.5</v>
+        <v>89.5</v>
       </c>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6" t="n"/>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="361" hidden="1" outlineLevel="2">
       <c r="A361" s="4" t="n">
-        <v>88.75</v>
+        <v>89.75</v>
       </c>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6" t="n"/>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="362" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A362" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6" t="n"/>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="363" hidden="1" outlineLevel="2">
       <c r="A363" s="4" t="n">
-        <v>89.25</v>
+        <v>90.25</v>
       </c>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6" t="n"/>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="364" hidden="1" outlineLevel="2">
       <c r="A364" s="4" t="n">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6" t="n"/>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="365" hidden="1" outlineLevel="2">
       <c r="A365" s="4" t="n">
-        <v>89.75</v>
+        <v>90.75</v>
       </c>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6" t="n"/>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="366" collapsed="1">
       <c r="A366" s="4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B366" s="5" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="367" hidden="1" outlineLevel="2">
       <c r="A367" s="4" t="n">
-        <v>90.25</v>
+        <v>91.25</v>
       </c>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6" t="n"/>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="368" hidden="1" outlineLevel="2">
       <c r="A368" s="4" t="n">
-        <v>90.5</v>
+        <v>91.5</v>
       </c>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6" t="n"/>
@@ -5005,7 +5005,7 @@
     </row>
     <row r="369" hidden="1" outlineLevel="2">
       <c r="A369" s="4" t="n">
-        <v>90.75</v>
+        <v>91.75</v>
       </c>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6" t="n"/>
@@ -5016,7 +5016,7 @@
     </row>
     <row r="370" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A370" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6" t="n"/>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="371" hidden="1" outlineLevel="2">
       <c r="A371" s="4" t="n">
-        <v>91.25</v>
+        <v>92.25</v>
       </c>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6" t="n"/>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="372" hidden="1" outlineLevel="2">
       <c r="A372" s="4" t="n">
-        <v>91.5</v>
+        <v>92.5</v>
       </c>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6" t="n"/>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="373" hidden="1" outlineLevel="2">
       <c r="A373" s="4" t="n">
-        <v>91.75</v>
+        <v>92.75</v>
       </c>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6" t="n"/>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="374" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A374" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6" t="n"/>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="375" hidden="1" outlineLevel="2">
       <c r="A375" s="4" t="n">
-        <v>92.25</v>
+        <v>93.25</v>
       </c>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6" t="n"/>
@@ -5082,7 +5082,7 @@
     </row>
     <row r="376" hidden="1" outlineLevel="2">
       <c r="A376" s="4" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6" t="n"/>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="377" hidden="1" outlineLevel="2">
       <c r="A377" s="4" t="n">
-        <v>92.75</v>
+        <v>93.75</v>
       </c>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6" t="n"/>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="378" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A378" s="4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6" t="n"/>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="379" hidden="1" outlineLevel="2">
       <c r="A379" s="4" t="n">
-        <v>93.25</v>
+        <v>94.25</v>
       </c>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6" t="n"/>
@@ -5126,7 +5126,7 @@
     </row>
     <row r="380" hidden="1" outlineLevel="2">
       <c r="A380" s="4" t="n">
-        <v>93.5</v>
+        <v>94.5</v>
       </c>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6" t="n"/>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="381" hidden="1" outlineLevel="2">
       <c r="A381" s="4" t="n">
-        <v>93.75</v>
+        <v>94.75</v>
       </c>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6" t="n"/>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="382" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A382" s="4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6" t="n"/>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="383" hidden="1" outlineLevel="2">
       <c r="A383" s="4" t="n">
-        <v>94.25</v>
+        <v>95.25</v>
       </c>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6" t="n"/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="384" hidden="1" outlineLevel="2">
       <c r="A384" s="4" t="n">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6" t="n"/>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="385" hidden="1" outlineLevel="2">
       <c r="A385" s="4" t="n">
-        <v>94.75</v>
+        <v>95.75</v>
       </c>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6" t="n"/>
@@ -5192,7 +5192,7 @@
     </row>
     <row r="386" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A386" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6" t="n"/>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="387" hidden="1" outlineLevel="2">
       <c r="A387" s="4" t="n">
-        <v>95.25</v>
+        <v>96.25</v>
       </c>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6" t="n"/>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="388" hidden="1" outlineLevel="2">
       <c r="A388" s="4" t="n">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6" t="n"/>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="389" hidden="1" outlineLevel="2">
       <c r="A389" s="4" t="n">
-        <v>95.75</v>
+        <v>96.75</v>
       </c>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6" t="n"/>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="390" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A390" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6" t="n"/>
@@ -5247,7 +5247,7 @@
     </row>
     <row r="391" hidden="1" outlineLevel="2">
       <c r="A391" s="4" t="n">
-        <v>96.25</v>
+        <v>97.25</v>
       </c>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6" t="n"/>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="392" hidden="1" outlineLevel="2">
       <c r="A392" s="4" t="n">
-        <v>96.5</v>
+        <v>97.5</v>
       </c>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6" t="n"/>
@@ -5269,7 +5269,7 @@
     </row>
     <row r="393" hidden="1" outlineLevel="2">
       <c r="A393" s="4" t="n">
-        <v>96.75</v>
+        <v>97.75</v>
       </c>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6" t="n"/>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="394" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A394" s="4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6" t="n"/>
@@ -5291,7 +5291,7 @@
     </row>
     <row r="395" hidden="1" outlineLevel="2">
       <c r="A395" s="4" t="n">
-        <v>97.25</v>
+        <v>98.25</v>
       </c>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6" t="n"/>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="396" hidden="1" outlineLevel="2">
       <c r="A396" s="4" t="n">
-        <v>97.5</v>
+        <v>98.5</v>
       </c>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6" t="n"/>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="397" hidden="1" outlineLevel="2">
       <c r="A397" s="4" t="n">
-        <v>97.75</v>
+        <v>98.75</v>
       </c>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6" t="n"/>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="398" collapsed="1">
       <c r="A398" s="4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B398" s="5" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="399" hidden="1" outlineLevel="2">
       <c r="A399" s="4" t="n">
-        <v>98.25</v>
+        <v>99.25</v>
       </c>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6" t="n"/>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="400" hidden="1" outlineLevel="2">
       <c r="A400" s="4" t="n">
-        <v>98.5</v>
+        <v>99.5</v>
       </c>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6" t="n"/>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="401" hidden="1" outlineLevel="2">
       <c r="A401" s="4" t="n">
-        <v>98.75</v>
+        <v>99.75</v>
       </c>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6" t="n"/>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="402" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A402" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6" t="n"/>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="403" hidden="1" outlineLevel="2">
       <c r="A403" s="4" t="n">
-        <v>99.25</v>
+        <v>100.25</v>
       </c>
       <c r="B403" s="5" t="n"/>
       <c r="C403" s="6" t="n"/>
@@ -5406,7 +5406,7 @@
     </row>
     <row r="404" hidden="1" outlineLevel="2">
       <c r="A404" s="4" t="n">
-        <v>99.5</v>
+        <v>100.5</v>
       </c>
       <c r="B404" s="5" t="n"/>
       <c r="C404" s="6" t="n"/>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="405" hidden="1" outlineLevel="2">
       <c r="A405" s="4" t="n">
-        <v>99.75</v>
+        <v>100.75</v>
       </c>
       <c r="B405" s="5" t="n"/>
       <c r="C405" s="6" t="n"/>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="406" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A406" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B406" s="5" t="n"/>
       <c r="C406" s="6" t="n"/>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="407" hidden="1" outlineLevel="2">
       <c r="A407" s="4" t="n">
-        <v>100.25</v>
+        <v>101.25</v>
       </c>
       <c r="B407" s="5" t="n"/>
       <c r="C407" s="6" t="n"/>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="408" hidden="1" outlineLevel="2">
       <c r="A408" s="4" t="n">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="B408" s="5" t="n"/>
       <c r="C408" s="6" t="n"/>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="409" hidden="1" outlineLevel="2">
       <c r="A409" s="4" t="n">
-        <v>100.75</v>
+        <v>101.75</v>
       </c>
       <c r="B409" s="5" t="n"/>
       <c r="C409" s="6" t="n"/>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="410" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A410" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B410" s="5" t="n"/>
       <c r="C410" s="6" t="n"/>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="411" hidden="1" outlineLevel="2">
       <c r="A411" s="4" t="n">
-        <v>101.25</v>
+        <v>102.25</v>
       </c>
       <c r="B411" s="5" t="n"/>
       <c r="C411" s="6" t="n"/>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="412" hidden="1" outlineLevel="2">
       <c r="A412" s="4" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="B412" s="5" t="n"/>
       <c r="C412" s="6" t="n"/>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="413" hidden="1" outlineLevel="2">
       <c r="A413" s="4" t="n">
-        <v>101.75</v>
+        <v>102.75</v>
       </c>
       <c r="B413" s="5" t="n"/>
       <c r="C413" s="6" t="n"/>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="414" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A414" s="4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B414" s="5" t="n"/>
       <c r="C414" s="6" t="n"/>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="415" hidden="1" outlineLevel="2">
       <c r="A415" s="4" t="n">
-        <v>102.25</v>
+        <v>103.25</v>
       </c>
       <c r="B415" s="5" t="n"/>
       <c r="C415" s="6" t="n"/>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="416" hidden="1" outlineLevel="2">
       <c r="A416" s="4" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="B416" s="5" t="n"/>
       <c r="C416" s="6" t="n"/>
@@ -5549,7 +5549,7 @@
     </row>
     <row r="417" hidden="1" outlineLevel="2">
       <c r="A417" s="4" t="n">
-        <v>102.75</v>
+        <v>103.75</v>
       </c>
       <c r="B417" s="5" t="n"/>
       <c r="C417" s="6" t="n"/>
@@ -5560,7 +5560,7 @@
     </row>
     <row r="418" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A418" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B418" s="5" t="n"/>
       <c r="C418" s="6" t="n"/>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="419" hidden="1" outlineLevel="2">
       <c r="A419" s="4" t="n">
-        <v>103.25</v>
+        <v>104.25</v>
       </c>
       <c r="B419" s="5" t="n"/>
       <c r="C419" s="6" t="n"/>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="420" hidden="1" outlineLevel="2">
       <c r="A420" s="4" t="n">
-        <v>103.5</v>
+        <v>104.5</v>
       </c>
       <c r="B420" s="5" t="n"/>
       <c r="C420" s="6" t="n"/>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="421" hidden="1" outlineLevel="2">
       <c r="A421" s="4" t="n">
-        <v>103.75</v>
+        <v>104.75</v>
       </c>
       <c r="B421" s="5" t="n"/>
       <c r="C421" s="6" t="n"/>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="422" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A422" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B422" s="5" t="n"/>
       <c r="C422" s="6" t="n"/>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="423" hidden="1" outlineLevel="2">
       <c r="A423" s="4" t="n">
-        <v>104.25</v>
+        <v>105.25</v>
       </c>
       <c r="B423" s="5" t="n"/>
       <c r="C423" s="6" t="n"/>
@@ -5626,7 +5626,7 @@
     </row>
     <row r="424" hidden="1" outlineLevel="2">
       <c r="A424" s="4" t="n">
-        <v>104.5</v>
+        <v>105.5</v>
       </c>
       <c r="B424" s="5" t="n"/>
       <c r="C424" s="6" t="n"/>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="425" hidden="1" outlineLevel="2">
       <c r="A425" s="4" t="n">
-        <v>104.75</v>
+        <v>105.75</v>
       </c>
       <c r="B425" s="5" t="n"/>
       <c r="C425" s="6" t="n"/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="426" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A426" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B426" s="5" t="n"/>
       <c r="C426" s="6" t="n"/>
@@ -5659,7 +5659,7 @@
     </row>
     <row r="427" hidden="1" outlineLevel="2">
       <c r="A427" s="4" t="n">
-        <v>105.25</v>
+        <v>106.25</v>
       </c>
       <c r="B427" s="5" t="n"/>
       <c r="C427" s="6" t="n"/>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="428" hidden="1" outlineLevel="2">
       <c r="A428" s="4" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="B428" s="5" t="n"/>
       <c r="C428" s="6" t="n"/>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="429" hidden="1" outlineLevel="2">
       <c r="A429" s="4" t="n">
-        <v>105.75</v>
+        <v>106.75</v>
       </c>
       <c r="B429" s="5" t="n"/>
       <c r="C429" s="6" t="n"/>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="430" collapsed="1">
       <c r="A430" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B430" s="5" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
     </row>
     <row r="431" hidden="1" outlineLevel="2">
       <c r="A431" s="4" t="n">
-        <v>106.25</v>
+        <v>107.25</v>
       </c>
       <c r="B431" s="5" t="n"/>
       <c r="C431" s="6" t="n"/>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="432" hidden="1" outlineLevel="2">
       <c r="A432" s="4" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="B432" s="5" t="n"/>
       <c r="C432" s="6" t="n"/>
@@ -5741,7 +5741,7 @@
     </row>
     <row r="433" hidden="1" outlineLevel="2">
       <c r="A433" s="4" t="n">
-        <v>106.75</v>
+        <v>107.75</v>
       </c>
       <c r="B433" s="5" t="n"/>
       <c r="C433" s="6" t="n"/>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="434" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A434" s="4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B434" s="5" t="n"/>
       <c r="C434" s="6" t="n"/>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="435" hidden="1" outlineLevel="2">
       <c r="A435" s="4" t="n">
-        <v>107.25</v>
+        <v>108.25</v>
       </c>
       <c r="B435" s="5" t="n"/>
       <c r="C435" s="6" t="n"/>
@@ -5774,7 +5774,7 @@
     </row>
     <row r="436" hidden="1" outlineLevel="2">
       <c r="A436" s="4" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="B436" s="5" t="n"/>
       <c r="C436" s="6" t="n"/>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="437" hidden="1" outlineLevel="2">
       <c r="A437" s="4" t="n">
-        <v>107.75</v>
+        <v>108.75</v>
       </c>
       <c r="B437" s="5" t="n"/>
       <c r="C437" s="6" t="n"/>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="438">
       <c r="A438" s="7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
